--- a/Deliverables/BOM/LCSC BOM.xlsx
+++ b/Deliverables/BOM/LCSC BOM.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\SH-CircuitCorrections\Deliverables\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9795"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="124">
   <si>
     <t>Bill of Material (BOM) for Stadium_Board</t>
   </si>
@@ -310,9 +315,6 @@
     <t>Aliexpress</t>
   </si>
   <si>
-    <t>Header</t>
-  </si>
-  <si>
     <t>500mA Jack DCPowerReceptacle 6.4mm 2.5mm 14.2*9.0mm AC/DC Power Connectors ROHS</t>
   </si>
   <si>
@@ -374,22 +376,33 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>----------</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
+    <t>win-source</t>
+  </si>
+  <si>
+    <t>Minimum Order Quantity =60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="179" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,62 +425,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -480,159 +438,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -653,7 +527,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,194 +543,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="34">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -894,7 +582,9 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -911,32 +601,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1095,17 +759,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1204,571 +857,376 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2026,1447 +1484,1481 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="80.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="25.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="22.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="30.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="29.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="15.2857142857143" customWidth="1"/>
-    <col min="9" max="9" width="16.7142857142857" customWidth="1"/>
-    <col min="11" max="12" width="23.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="23.2857142857143" customWidth="1"/>
-    <col min="15" max="15" width="24.5714285714286" customWidth="1"/>
-    <col min="16" max="16" width="10.5714285714286" customWidth="1"/>
-    <col min="17" max="17" width="13.4285714285714" customWidth="1"/>
-    <col min="18" max="18" width="14.2857142857143" customWidth="1"/>
-    <col min="19" max="20" width="22.1428571428571" customWidth="1"/>
-    <col min="21" max="21" width="23.4285714285714" customWidth="1"/>
+    <col min="14" max="14" width="23.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.140625" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.42578125" customWidth="1"/>
     <col min="22" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="24.7142857142857" customWidth="1"/>
-    <col min="25" max="25" width="17.5714285714286" customWidth="1"/>
-    <col min="26" max="26" width="19.5714285714286" customWidth="1"/>
+    <col min="24" max="24" width="24.7109375" customWidth="1"/>
+    <col min="25" max="25" width="17.5703125" customWidth="1"/>
+    <col min="26" max="26" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:26">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="67"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="9"/>
     </row>
-    <row r="2" ht="16.5" spans="1:26">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" s="80" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:27">
-      <c r="A3" s="5">
+    <row r="3" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A3" s="80">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="77" t="s">
+      <c r="H3" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="84">
         <v>1</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="86">
         <f>K3*5</f>
         <v>5</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="86">
         <f>K3*20</f>
         <v>20</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="86">
         <f>K3*100</f>
         <v>100</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="86">
         <v>120</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="58">
+      <c r="Q3" s="88">
         <v>0.05</v>
       </c>
-      <c r="R3" s="58">
+      <c r="R3" s="88">
         <f>Q3*K3</f>
         <v>0.05</v>
       </c>
-      <c r="S3" s="58">
+      <c r="S3" s="88">
         <v>0.05</v>
       </c>
-      <c r="T3" s="58">
+      <c r="T3" s="88">
         <f>S3*L3</f>
         <v>0.25</v>
       </c>
-      <c r="U3" s="58">
+      <c r="U3" s="88">
         <v>0.05</v>
       </c>
-      <c r="V3" s="58">
+      <c r="V3" s="88">
         <f>U3*M3</f>
         <v>1</v>
       </c>
-      <c r="W3" s="58">
-        <f>Q3*O3</f>
+      <c r="W3" s="88">
+        <f>X3*O3</f>
         <v>6</v>
       </c>
-      <c r="X3" s="58">
+      <c r="X3" s="88">
         <v>0.05</v>
       </c>
-      <c r="Y3" s="58">
+      <c r="Y3" s="88">
         <f>X3*N3</f>
         <v>5</v>
       </c>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="69"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="5"/>
     </row>
-    <row r="4" ht="15.75" spans="1:27">
-      <c r="A4" s="5">
+    <row r="4" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A4" s="80">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="78" t="s">
+      <c r="C4" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="79" t="s">
+      <c r="I4" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="32">
         <v>1</v>
       </c>
-      <c r="L4" s="41">
-        <f t="shared" ref="L4:L17" si="0">K4*5</f>
+      <c r="L4" s="33">
+        <f t="shared" ref="L4:L15" si="0">K4*5</f>
         <v>5</v>
       </c>
-      <c r="M4" s="41">
-        <f t="shared" ref="M4:M17" si="1">K4*20</f>
+      <c r="M4" s="33">
+        <f t="shared" ref="M4:M15" si="1">K4*20</f>
         <v>20</v>
       </c>
-      <c r="N4" s="41">
-        <f t="shared" ref="N4:N17" si="2">K4*100</f>
+      <c r="N4" s="33">
+        <f t="shared" ref="N4:N15" si="2">K4*100</f>
         <v>100</v>
       </c>
-      <c r="O4" s="41">
+      <c r="O4" s="33">
         <v>150</v>
       </c>
-      <c r="P4" s="42" t="s">
+      <c r="P4" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="59">
+      <c r="Q4" s="35">
         <v>0.01</v>
       </c>
-      <c r="R4" s="59">
+      <c r="R4" s="35">
         <f t="shared" ref="R4:R15" si="3">Q4*K4</f>
         <v>0.01</v>
       </c>
-      <c r="S4" s="59">
+      <c r="S4" s="35">
         <v>0.01</v>
       </c>
-      <c r="T4" s="59">
+      <c r="T4" s="35">
         <f t="shared" ref="T4:T15" si="4">S4*L4</f>
         <v>0.05</v>
       </c>
-      <c r="U4" s="59">
+      <c r="U4" s="35">
         <v>0.01</v>
       </c>
-      <c r="V4" s="59">
+      <c r="V4" s="35">
         <f t="shared" ref="V4:V15" si="5">U4*M4</f>
         <v>0.2</v>
       </c>
-      <c r="W4" s="59">
-        <f t="shared" ref="W4:W15" si="6">Q4*O4</f>
+      <c r="W4" s="35">
+        <f t="shared" ref="W4:W14" si="6">X4*O4</f>
         <v>1.5</v>
       </c>
-      <c r="X4" s="59">
+      <c r="X4" s="35">
         <v>0.01</v>
       </c>
-      <c r="Y4" s="59">
+      <c r="Y4" s="35">
         <f t="shared" ref="Y4:Y15" si="7">X4*N4</f>
         <v>1</v>
       </c>
-      <c r="Z4" s="70"/>
-      <c r="AA4" s="69"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="5"/>
     </row>
-    <row r="5" ht="16.5" spans="1:27">
-      <c r="A5" s="5">
+    <row r="5" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A5" s="80">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="80" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="81" t="s">
+      <c r="G5" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="43"/>
-      <c r="J5" s="81" t="s">
+      <c r="I5" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="J5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="41">
         <v>3</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="42">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="42">
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="42">
         <v>320</v>
       </c>
-      <c r="P5" s="44" t="s">
+      <c r="P5" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="Q5" s="60">
-        <v>0.0283</v>
-      </c>
-      <c r="R5" s="60">
+      <c r="Q5" s="44">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="R5" s="44">
         <f t="shared" si="3"/>
-        <v>0.0849</v>
-      </c>
-      <c r="S5" s="60">
-        <v>0.0283</v>
-      </c>
-      <c r="T5" s="60">
+        <v>8.4900000000000003E-2</v>
+      </c>
+      <c r="S5" s="44">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="T5" s="44">
         <f t="shared" si="4"/>
-        <v>0.4245</v>
-      </c>
-      <c r="U5" s="60">
-        <v>0.0283</v>
-      </c>
-      <c r="V5" s="60">
+        <v>0.42449999999999999</v>
+      </c>
+      <c r="U5" s="44">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="V5" s="44">
         <f t="shared" si="5"/>
         <v>1.698</v>
       </c>
-      <c r="W5" s="60">
+      <c r="W5" s="44">
         <f t="shared" si="6"/>
-        <v>9.056</v>
-      </c>
-      <c r="X5" s="60">
-        <v>0.0209</v>
-      </c>
-      <c r="Y5" s="60">
+        <v>6.6879999999999997</v>
+      </c>
+      <c r="X5" s="44">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="Y5" s="44">
         <f t="shared" si="7"/>
         <v>6.27</v>
       </c>
-      <c r="Z5" s="71"/>
-      <c r="AA5" s="69"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="5"/>
     </row>
-    <row r="6" ht="16.5" spans="1:27">
-      <c r="A6" s="5">
+    <row r="6" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A6" s="80">
         <v>4</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="77" t="s">
+      <c r="G6" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="77" t="s">
+      <c r="H6" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="23">
         <v>2</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="25">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="25">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="25">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="25">
         <v>220</v>
       </c>
-      <c r="P6" s="45" t="s">
+      <c r="P6" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="26">
         <v>2.96</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="26">
         <f t="shared" si="3"/>
         <v>5.92</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="26">
         <v>2.96</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="26">
         <f t="shared" si="4"/>
         <v>29.6</v>
       </c>
-      <c r="U6" s="58">
+      <c r="U6" s="26">
         <v>2.96</v>
       </c>
-      <c r="V6" s="58">
+      <c r="V6" s="26">
         <f t="shared" si="5"/>
         <v>118.4</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="26">
         <f t="shared" si="6"/>
-        <v>651.2</v>
-      </c>
-      <c r="X6" s="58">
+        <v>651.20000000000005</v>
+      </c>
+      <c r="X6" s="26">
         <v>2.96</v>
       </c>
-      <c r="Y6" s="58">
+      <c r="Y6" s="26">
         <f t="shared" si="7"/>
         <v>592</v>
       </c>
-      <c r="Z6" s="68"/>
-      <c r="AA6" s="69"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="5"/>
     </row>
-    <row r="7" ht="16.5" spans="1:27">
-      <c r="A7" s="5">
+    <row r="7" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A7" s="80">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="77" t="s">
+      <c r="I7" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="84">
         <v>2</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="86">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="86">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="86">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="O7" s="9">
-        <v>220</v>
-      </c>
-      <c r="P7" s="45" t="s">
+      <c r="O7" s="86">
+        <v>210</v>
+      </c>
+      <c r="P7" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="58" t="s">
+      <c r="Q7" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="58">
-        <f t="shared" si="3"/>
-        <v>0.8152</v>
-      </c>
-      <c r="S7" s="58">
-        <v>0.3174</v>
-      </c>
-      <c r="T7" s="58">
+      <c r="R7" s="88">
+        <v>0.82</v>
+      </c>
+      <c r="S7" s="88">
+        <v>0.31740000000000002</v>
+      </c>
+      <c r="T7" s="88">
         <f t="shared" si="4"/>
-        <v>3.174</v>
-      </c>
-      <c r="U7" s="58">
-        <v>0.3012</v>
-      </c>
-      <c r="V7" s="58">
+        <v>3.1740000000000004</v>
+      </c>
+      <c r="U7" s="88">
+        <v>0.30120000000000002</v>
+      </c>
+      <c r="V7" s="88">
         <f t="shared" si="5"/>
-        <v>12.048</v>
-      </c>
-      <c r="W7" s="58">
+        <v>12.048000000000002</v>
+      </c>
+      <c r="W7" s="88">
         <f t="shared" si="6"/>
-        <v>89.672</v>
-      </c>
-      <c r="X7" s="58">
-        <v>0.2832</v>
-      </c>
-      <c r="Y7" s="58">
+        <v>59.472000000000001</v>
+      </c>
+      <c r="X7" s="88">
+        <v>0.28320000000000001</v>
+      </c>
+      <c r="Y7" s="88">
         <f t="shared" si="7"/>
         <v>56.64</v>
       </c>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="69"/>
+      <c r="Z7" s="89"/>
+      <c r="AA7" s="5"/>
     </row>
-    <row r="8" ht="15.75" spans="1:27">
-      <c r="A8" s="5">
+    <row r="8" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A8" s="80">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="79" t="s">
+      <c r="E8" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="79" t="s">
+      <c r="F8" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="41"/>
-      <c r="J8" s="79" t="s">
+      <c r="I8" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="32">
         <v>2</v>
       </c>
-      <c r="L8" s="41">
+      <c r="L8" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M8" s="41">
+      <c r="M8" s="33">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N8" s="41">
+      <c r="N8" s="33">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="O8" s="41">
+      <c r="O8" s="33">
         <v>250</v>
       </c>
-      <c r="P8" s="46" t="s">
+      <c r="P8" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="Q8" s="59">
-        <v>0.0118</v>
-      </c>
-      <c r="R8" s="59">
+      <c r="Q8" s="35">
+        <v>1.18E-2</v>
+      </c>
+      <c r="R8" s="35">
         <f t="shared" si="3"/>
-        <v>0.0236</v>
-      </c>
-      <c r="S8" s="59">
-        <v>0.0118</v>
-      </c>
-      <c r="T8" s="59">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="S8" s="35">
+        <v>1.18E-2</v>
+      </c>
+      <c r="T8" s="35">
         <f t="shared" si="4"/>
-        <v>0.118</v>
-      </c>
-      <c r="U8" s="59">
-        <v>0.0118</v>
-      </c>
-      <c r="V8" s="59">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="U8" s="35">
+        <v>1.18E-2</v>
+      </c>
+      <c r="V8" s="35">
         <f t="shared" si="5"/>
-        <v>0.472</v>
-      </c>
-      <c r="W8" s="59">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="W8" s="35">
         <f t="shared" si="6"/>
-        <v>2.95</v>
-      </c>
-      <c r="X8" s="59">
-        <v>0.0118</v>
-      </c>
-      <c r="Y8" s="59">
+        <v>2.9499999999999997</v>
+      </c>
+      <c r="X8" s="35">
+        <v>1.18E-2</v>
+      </c>
+      <c r="Y8" s="35">
         <f t="shared" si="7"/>
         <v>2.36</v>
       </c>
-      <c r="Z8" s="70"/>
-      <c r="AA8" s="69"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="5"/>
     </row>
-    <row r="9" ht="15.75" spans="1:27">
-      <c r="A9" s="5">
+    <row r="9" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A9" s="98">
         <v>7</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="82" t="s">
+      <c r="G9" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="47"/>
-      <c r="J9" s="82" t="s">
+      <c r="I9" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="J9" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="52">
         <v>6</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="53">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="53">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="N9" s="47">
+      <c r="N9" s="53">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
-      <c r="O9" s="47">
+      <c r="O9" s="53">
         <v>700</v>
       </c>
-      <c r="P9" s="48" t="s">
+      <c r="P9" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="Q9" s="61">
-        <v>0.0024</v>
-      </c>
-      <c r="R9" s="61">
+      <c r="Q9" s="55">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="R9" s="55">
         <f t="shared" si="3"/>
-        <v>0.0144</v>
-      </c>
-      <c r="S9" s="61">
-        <v>0.0024</v>
-      </c>
-      <c r="T9" s="61">
+        <v>1.44E-2</v>
+      </c>
+      <c r="S9" s="55">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="T9" s="55">
         <f t="shared" si="4"/>
-        <v>0.072</v>
-      </c>
-      <c r="U9" s="61">
-        <v>0.0024</v>
-      </c>
-      <c r="V9" s="61">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="U9" s="55">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="V9" s="55">
         <f t="shared" si="5"/>
-        <v>0.288</v>
-      </c>
-      <c r="W9" s="61">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="W9" s="55">
         <f t="shared" si="6"/>
         <v>1.68</v>
       </c>
-      <c r="X9" s="61">
-        <v>0.0024</v>
-      </c>
-      <c r="Y9" s="61">
+      <c r="X9" s="55">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Y9" s="55">
         <f t="shared" si="7"/>
         <v>1.44</v>
       </c>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="69"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="5"/>
     </row>
-    <row r="10" ht="15.75" spans="1:27">
-      <c r="A10" s="5">
+    <row r="10" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A10" s="80">
         <v>8</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="82" t="s">
+      <c r="E10" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="82" t="s">
+      <c r="G10" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="52">
         <v>6</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="53">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="53">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="N10" s="47">
+      <c r="N10" s="53">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
-      <c r="O10" s="47">
-        <v>620</v>
-      </c>
-      <c r="P10" s="49" t="s">
+      <c r="O10" s="53">
+        <v>610</v>
+      </c>
+      <c r="P10" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="61">
-        <v>0.177</v>
-      </c>
-      <c r="R10" s="61">
+      <c r="Q10" s="55">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="R10" s="55">
         <f t="shared" si="3"/>
-        <v>1.062</v>
-      </c>
-      <c r="S10" s="61">
+        <v>1.0619999999999998</v>
+      </c>
+      <c r="S10" s="55">
         <v>0.1217</v>
       </c>
-      <c r="T10" s="61">
+      <c r="T10" s="55">
         <f t="shared" si="4"/>
-        <v>3.651</v>
-      </c>
-      <c r="U10" s="61">
+        <v>3.6510000000000002</v>
+      </c>
+      <c r="U10" s="55">
         <v>0.1132</v>
       </c>
-      <c r="V10" s="61">
+      <c r="V10" s="55">
         <f t="shared" si="5"/>
         <v>13.584</v>
       </c>
-      <c r="W10" s="61">
+      <c r="W10" s="55">
         <f t="shared" si="6"/>
-        <v>109.74</v>
-      </c>
-      <c r="X10" s="61">
+        <v>66.733999999999995</v>
+      </c>
+      <c r="X10" s="55">
         <v>0.1094</v>
       </c>
-      <c r="Y10" s="61">
+      <c r="Y10" s="55">
         <f t="shared" si="7"/>
         <v>65.64</v>
       </c>
-      <c r="Z10" s="73" t="s">
+      <c r="Z10" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="AA10" s="69"/>
+      <c r="AA10" s="5"/>
     </row>
-    <row r="11" ht="16.5" spans="1:27">
-      <c r="A11" s="5">
+    <row r="11" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A11" s="80">
         <v>9</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="81" t="s">
+      <c r="E11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="81" t="s">
+      <c r="G11" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="81" t="s">
+      <c r="J11" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="41">
         <v>2</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="42">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="42">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N11" s="43">
+      <c r="N11" s="42">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="42">
         <v>250</v>
       </c>
-      <c r="P11" s="50" t="s">
+      <c r="P11" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="Q11" s="60">
-        <v>0.0107</v>
-      </c>
-      <c r="R11" s="60">
+      <c r="Q11" s="44">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="R11" s="44">
         <f t="shared" si="3"/>
-        <v>0.0214</v>
-      </c>
-      <c r="S11" s="60">
-        <v>0.0107</v>
-      </c>
-      <c r="T11" s="60">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="S11" s="44">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="T11" s="44">
         <f t="shared" si="4"/>
         <v>0.107</v>
       </c>
-      <c r="U11" s="60">
-        <v>0.0107</v>
-      </c>
-      <c r="V11" s="60">
+      <c r="U11" s="44">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="V11" s="44">
         <f t="shared" si="5"/>
-        <v>0.428</v>
-      </c>
-      <c r="W11" s="60">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="W11" s="44">
         <f t="shared" si="6"/>
-        <v>2.675</v>
-      </c>
-      <c r="X11" s="60">
-        <v>0.0107</v>
-      </c>
-      <c r="Y11" s="60">
+        <v>2.6749999999999998</v>
+      </c>
+      <c r="X11" s="44">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="Y11" s="44">
         <f t="shared" si="7"/>
-        <v>2.14</v>
-      </c>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="69"/>
+        <v>2.1399999999999997</v>
+      </c>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="5"/>
     </row>
-    <row r="12" ht="16.5" spans="1:27">
-      <c r="A12" s="5">
+    <row r="12" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A12" s="80">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="77" t="s">
+      <c r="D12" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="77" t="s">
+      <c r="G12" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="77" t="s">
+      <c r="H12" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="84">
         <v>2</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="86">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="86">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="86">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="86">
         <v>220</v>
       </c>
-      <c r="P12" s="40" t="s">
+      <c r="P12" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="Q12" s="58">
+      <c r="Q12" s="88">
         <v>0.2</v>
       </c>
-      <c r="R12" s="58">
+      <c r="R12" s="88">
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="S12" s="58">
+      <c r="S12" s="88">
         <v>0.2</v>
       </c>
-      <c r="T12" s="58">
+      <c r="T12" s="88">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="U12" s="58">
+      <c r="U12" s="88">
         <v>0.2</v>
       </c>
-      <c r="V12" s="58">
+      <c r="V12" s="88">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="W12" s="58">
+      <c r="W12" s="88">
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="X12" s="58">
+      <c r="X12" s="88">
         <v>0.2</v>
       </c>
-      <c r="Y12" s="58">
+      <c r="Y12" s="88">
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="Z12" s="68"/>
-      <c r="AA12" s="69"/>
+      <c r="Z12" s="89"/>
+      <c r="AA12" s="5"/>
     </row>
-    <row r="13" ht="15.75" spans="1:27">
-      <c r="A13" s="5">
+    <row r="13" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A13" s="80">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="D13" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="79" t="s">
+      <c r="E13" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="79" t="s">
+      <c r="G13" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="G13" s="79" t="s">
+      <c r="H13" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="41"/>
-      <c r="J13" s="79" t="s">
+      <c r="I13" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="32">
         <v>1</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="33">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="33">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="O13" s="41">
+      <c r="O13" s="33">
         <v>120</v>
       </c>
-      <c r="P13" s="46" t="s">
+      <c r="P13" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="59">
-        <v>0.0952</v>
-      </c>
-      <c r="R13" s="59">
+      <c r="Q13" s="35">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="R13" s="35">
         <f t="shared" si="3"/>
-        <v>0.0952</v>
-      </c>
-      <c r="S13" s="59">
-        <v>0.0952</v>
-      </c>
-      <c r="T13" s="59">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="S13" s="35">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="T13" s="35">
         <f t="shared" si="4"/>
-        <v>0.476</v>
-      </c>
-      <c r="U13" s="59">
-        <v>0.0952</v>
-      </c>
-      <c r="V13" s="59">
+        <v>0.47600000000000003</v>
+      </c>
+      <c r="U13" s="35">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="V13" s="35">
         <f t="shared" si="5"/>
-        <v>1.904</v>
-      </c>
-      <c r="W13" s="59">
+        <v>1.9040000000000001</v>
+      </c>
+      <c r="W13" s="35">
         <f t="shared" si="6"/>
-        <v>11.424</v>
-      </c>
-      <c r="X13" s="59">
-        <v>0.07</v>
-      </c>
-      <c r="Y13" s="59">
+        <v>8.4</v>
+      </c>
+      <c r="X13" s="35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Y13" s="35">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Z13" s="70"/>
-      <c r="AA13" s="69"/>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="5"/>
     </row>
-    <row r="14" ht="15.75" spans="1:27">
-      <c r="A14" s="5">
+    <row r="14" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A14" s="80">
         <v>12</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="27" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="82" t="s">
+      <c r="E14" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="82" t="s">
+      <c r="G14" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="82" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="82" t="s">
+      <c r="H14" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="52">
         <v>1</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="53">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="53">
         <v>120</v>
       </c>
-      <c r="P14" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q14" s="61">
-        <v>4</v>
-      </c>
-      <c r="R14" s="61">
+      <c r="P14" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q14" s="55">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="R14" s="55">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="S14" s="61">
-        <v>4</v>
-      </c>
-      <c r="T14" s="61">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="S14" s="55">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="T14" s="55">
         <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="U14" s="61">
-        <v>4</v>
-      </c>
-      <c r="V14" s="61">
+        <v>4.5350000000000001</v>
+      </c>
+      <c r="U14" s="55">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="V14" s="55">
         <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="W14" s="61">
+        <v>18.14</v>
+      </c>
+      <c r="W14" s="55">
         <f t="shared" si="6"/>
-        <v>480</v>
-      </c>
-      <c r="X14" s="61">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="61">
+        <v>108.84</v>
+      </c>
+      <c r="X14" s="55">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="Y14" s="55">
         <f t="shared" si="7"/>
-        <v>400</v>
-      </c>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="69"/>
+        <v>90.7</v>
+      </c>
+      <c r="Z14" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA14" s="5"/>
     </row>
-    <row r="15" ht="15.75" spans="1:27">
-      <c r="A15" s="5">
+    <row r="15" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A15" s="80">
         <v>13</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="83" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="84" t="s">
+      <c r="E15" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="84" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="84" t="s">
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="64">
         <v>1</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="64">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N15" s="30">
+      <c r="N15" s="64">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62">
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S15" s="62"/>
-      <c r="T15" s="62">
+      <c r="S15" s="65"/>
+      <c r="T15" s="65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U15" s="62"/>
-      <c r="V15" s="62">
+      <c r="U15" s="65"/>
+      <c r="V15" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W15" s="62">
-        <f t="shared" si="6"/>
+      <c r="W15" s="65">
+        <f t="shared" ref="W4:W15" si="8">Q15*O15</f>
         <v>0</v>
       </c>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62">
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="73" t="s">
+      <c r="Z15" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA15" s="5"/>
+    </row>
+    <row r="16" spans="1:27" ht="16.5" thickBot="1">
+      <c r="A16" s="80">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="AA15" s="69"/>
+      <c r="D16" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="94">
+        <v>2</v>
+      </c>
+      <c r="L16" s="94">
+        <v>10</v>
+      </c>
+      <c r="M16" s="94">
+        <v>40</v>
+      </c>
+      <c r="N16" s="94">
+        <v>200</v>
+      </c>
+      <c r="O16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P16" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="R16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="S16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="T16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="U16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="V16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="W16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="X16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y16" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z16" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA16" s="5"/>
     </row>
-    <row r="16" ht="15.75" spans="1:27">
-      <c r="A16" s="5">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="32" t="s">
+    <row r="17" spans="1:26" ht="16.5" thickBot="1">
+      <c r="A17" s="80">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="96" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="34" t="s">
+      <c r="G17" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" s="96">
+        <v>7</v>
+      </c>
+      <c r="L17" s="96">
+        <v>35</v>
+      </c>
+      <c r="M17" s="96">
+        <v>140</v>
+      </c>
+      <c r="N17" s="96">
+        <v>700</v>
+      </c>
+      <c r="O17" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="P17" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="R17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="S17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="T17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="U17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="V17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="W17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="X17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y17" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z17" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="J16" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="K16" s="32">
-        <v>2</v>
-      </c>
-      <c r="L16" s="32">
-        <v>10</v>
-      </c>
-      <c r="M16" s="32">
-        <v>40</v>
-      </c>
-      <c r="N16" s="32">
-        <v>200</v>
-      </c>
-      <c r="O16" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="P16" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="R16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="S16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="T16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="U16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="V16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="W16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="X16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z16" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA16" s="69"/>
     </row>
-    <row r="17" ht="16.5" spans="1:26">
-      <c r="A17" s="5">
-        <v>15</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="36" t="s">
+    <row r="18" spans="1:26" ht="21.75" thickBot="1">
+      <c r="D18" s="2"/>
+      <c r="K18" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" s="86" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="36">
-        <v>7</v>
-      </c>
-      <c r="L17" s="36">
-        <v>35</v>
-      </c>
-      <c r="M17" s="36">
-        <v>140</v>
-      </c>
-      <c r="N17" s="36">
-        <v>700</v>
-      </c>
-      <c r="O17" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="P17" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="R17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="S17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="T17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="U17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="V17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="W17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="X17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z17" s="75" t="s">
-        <v>115</v>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="4">
+        <f>SUM(T3:T15)</f>
+        <v>44.45750000000001</v>
+      </c>
+      <c r="U18" s="3"/>
+      <c r="V18" s="4">
+        <f>SUM(V3:V15)</f>
+        <v>176.16200000000003</v>
+      </c>
+      <c r="W18" s="4">
+        <f>SUM(W3:W15)</f>
+        <v>960.13900000000001</v>
+      </c>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="4">
+        <f>SUM(Y3:Y15)</f>
+        <v>870.19</v>
       </c>
     </row>
-    <row r="18" ht="21.75" spans="4:25">
-      <c r="D18" s="39"/>
-      <c r="K18" s="55" t="s">
+    <row r="19" spans="1:26" ht="21">
+      <c r="K19" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="66">
-        <f>SUM(T3:T15)</f>
-        <v>59.9225</v>
-      </c>
-      <c r="U18" s="65"/>
-      <c r="V18" s="66">
-        <f>SUM(V3:V15)</f>
-        <v>238.022</v>
-      </c>
-      <c r="W18" s="66">
-        <f>SUM(W3:W15)</f>
-        <v>1409.897</v>
-      </c>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="66">
-        <f>SUM(Y3:Y15)</f>
-        <v>1179.49</v>
-      </c>
-    </row>
-    <row r="19" ht="21" spans="11:26">
-      <c r="K19" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="L19" s="56"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="56"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="66">
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="4">
         <f>SUM(R3:R15)</f>
-        <v>12.4967</v>
-      </c>
-      <c r="S19" s="65"/>
-      <c r="T19" s="66">
+        <v>9.4085000000000001</v>
+      </c>
+      <c r="S19" s="3"/>
+      <c r="T19" s="4">
         <f>T18/5</f>
-        <v>11.9845</v>
-      </c>
-      <c r="U19" s="65"/>
-      <c r="V19" s="66">
+        <v>8.8915000000000024</v>
+      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="4">
         <f>V18/20</f>
-        <v>11.9011</v>
-      </c>
-      <c r="W19" s="66">
+        <v>8.8081000000000014</v>
+      </c>
+      <c r="W19" s="4">
         <f>W18/100</f>
-        <v>14.09897</v>
-      </c>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="66">
+        <v>9.6013900000000003</v>
+      </c>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="4">
         <f>Y18/100</f>
-        <v>11.7949</v>
-      </c>
-      <c r="Z19" s="65"/>
+        <v>8.7019000000000002</v>
+      </c>
+      <c r="Z19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3486,7 +2978,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d710f97-1bf7-4784-894e-1861056f6628}</x14:id>
+          <x14:id>{5D710F97-1BF7-4784-894E-1861056F6628}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3500,7 +2992,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0e5c7ab-ae3e-4dac-94d8-975e90381f46}</x14:id>
+          <x14:id>{E0E5C7AB-AE3E-4DAC-94D8-975E90381F46}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3514,7 +3006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17634760-f266-4682-89c5-eb5f05e41d77}</x14:id>
+          <x14:id>{17634760-F266-4682-89C5-EB5F05E41D77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3528,7 +3020,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e17ecb40-d5e3-4565-a969-683333b81809}</x14:id>
+          <x14:id>{E17ECB40-D5E3-4565-A969-683333B81809}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3542,7 +3034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55660422-6c30-4a05-a6c1-dcc473a0984e}</x14:id>
+          <x14:id>{55660422-6C30-4A05-A6C1-DCC473A0984E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3556,7 +3048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ccb8173-a81f-4795-af77-04beef2e5035}</x14:id>
+          <x14:id>{0CCB8173-A81F-4795-AF77-04BEEF2E5035}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3570,7 +3062,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{962429e8-f0bd-4e9f-bc8e-39cad2b910fc}</x14:id>
+          <x14:id>{962429E8-F0BD-4E9F-BC8E-39CAD2B910FC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3588,26 +3080,26 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P5" r:id="rId1" display="LCSC"/>
-    <hyperlink ref="P7" r:id="rId2" display="LCSC"/>
-    <hyperlink ref="P8" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="P9" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="P13" r:id="rId5" display="LCSC"/>
-    <hyperlink ref="P4" r:id="rId6" display="LCSC"/>
-    <hyperlink ref="P6" r:id="rId7" display="IC-Chip"/>
-    <hyperlink ref="P14" r:id="rId8" display="Aliexpress"/>
-    <hyperlink ref="P12" r:id="rId9" display="Aliexpress"/>
-    <hyperlink ref="P10" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="P11" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="P3" r:id="rId12" display="DGSER"/>
+    <hyperlink ref="P5" r:id="rId1"/>
+    <hyperlink ref="P7" r:id="rId2"/>
+    <hyperlink ref="P8" r:id="rId3"/>
+    <hyperlink ref="P9" r:id="rId4"/>
+    <hyperlink ref="P13" r:id="rId5"/>
+    <hyperlink ref="P4" r:id="rId6"/>
+    <hyperlink ref="P6" r:id="rId7"/>
+    <hyperlink ref="P12" r:id="rId8"/>
+    <hyperlink ref="P10" r:id="rId9"/>
+    <hyperlink ref="P11" r:id="rId10"/>
+    <hyperlink ref="P3" r:id="rId11"/>
+    <hyperlink ref="P14" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d710f97-1bf7-4784-894e-1861056f6628}">
+          <x14:cfRule type="dataBar" id="{5D710F97-1BF7-4784-894E-1861056F6628}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3620,7 +3112,7 @@
           <xm:sqref>T18:Z18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e0e5c7ab-ae3e-4dac-94d8-975e90381f46}">
+          <x14:cfRule type="dataBar" id="{E0E5C7AB-AE3E-4DAC-94D8-975E90381F46}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3633,7 +3125,7 @@
           <xm:sqref>R19:Z19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17634760-f266-4682-89c5-eb5f05e41d77}">
+          <x14:cfRule type="dataBar" id="{17634760-F266-4682-89C5-EB5F05E41D77}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3646,7 +3138,7 @@
           <xm:sqref>R3:R15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e17ecb40-d5e3-4565-a969-683333b81809}">
+          <x14:cfRule type="dataBar" id="{E17ECB40-D5E3-4565-A969-683333B81809}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3659,7 +3151,7 @@
           <xm:sqref>T3:T15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55660422-6c30-4a05-a6c1-dcc473a0984e}">
+          <x14:cfRule type="dataBar" id="{55660422-6C30-4A05-A6C1-DCC473A0984E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3672,7 +3164,7 @@
           <xm:sqref>V3:V15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0ccb8173-a81f-4795-af77-04beef2e5035}">
+          <x14:cfRule type="dataBar" id="{0CCB8173-A81F-4795-AF77-04BEEF2E5035}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3685,7 +3177,7 @@
           <xm:sqref>W3:W15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{962429e8-f0bd-4e9f-bc8e-39cad2b910fc}">
+          <x14:cfRule type="dataBar" id="{962429E8-F0BD-4E9F-BC8E-39CAD2B910FC}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
